--- a/data/testcase.xlsx
+++ b/data/testcase.xlsx
@@ -1,33 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="22624"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Desktop\Romens_Api_Test\data\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4E4ACEC-6A07-4B90-928B-0A0079D5813A}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
-  <bookViews>
-    <workbookView xWindow="-1905" yWindow="975" windowWidth="29010" windowHeight="10455" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
-  </bookViews>
-  <sheets>
-    <sheet name="ORGGUID" sheetId="1" r:id="rId1"/>
-    <sheet name="PHONE" sheetId="2" r:id="rId2"/>
-    <sheet name="DEVICEID" sheetId="3" r:id="rId3"/>
-  </sheets>
-  <calcPr calcId="162913"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-  </extLst>
-</workbook>
+<s:workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:s="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <s:workbookPr codeName="ThisWorkbook"/>
+  <s:bookViews>
+    <s:workbookView activeTab="0"/>
+  </s:bookViews>
+  <s:sheets>
+    <s:sheet name="ORGGUID" sheetId="1" r:id="rId1"/>
+    <s:sheet name="PHONE" sheetId="2" r:id="rId2"/>
+    <s:sheet name="PWD" sheetId="3" r:id="rId3"/>
+  </s:sheets>
+  <s:definedNames/>
+  <s:calcPr calcId="124519" fullCalcOnLoad="1"/>
+</s:workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="50">
   <si>
     <t>case_id</t>
   </si>
@@ -56,41 +45,154 @@
     <t>check_sql</t>
   </si>
   <si>
+    <t>orggiud</t>
+  </si>
+  <si>
+    <t>App验证企业号-验证成功</t>
+  </si>
+  <si>
     <t>post</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>orggiud</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>/login</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"QueryType": "checkOrgCode", "Params": '{"ORGGUID": "#ORGGUID#", "AppName": "com.romens.health.pharmacy.client"}'}</t>
+  </si>
+  <si>
+    <t>{'result': '0000', 'msg': '验证成功'}</t>
+  </si>
+  <si>
+    <t>通过</t>
+  </si>
+  <si>
+    <t>App验证企业号-企业号为空</t>
+  </si>
+  <si>
+    <t>{"QueryType": "checkOrgCode", "Params": '{"ORGGUID": "", "AppName": "com.romens.health.pharmacy.client"}'}</t>
+  </si>
+  <si>
+    <t>{'result': '0001', 'msg': '验证失败'}</t>
+  </si>
+  <si>
+    <t>App验证企业号-QueryType为空</t>
+  </si>
+  <si>
+    <t>{"QueryType": "", "Params": '{"ORGGUID": "#ORGGUID#", "AppName": "com.romens.health.pharmacy.client"}'}</t>
+  </si>
+  <si>
+    <t>{'result': 'error', 'msg': 'WRONG HANDLERNAME！'}</t>
+  </si>
+  <si>
+    <t>App验证企业号-AppName为空</t>
+  </si>
+  <si>
+    <t>{"QueryType": "checkOrgCode", "Params": '{"ORGGUID": "#ORGGUID#", "AppName": ""}'}</t>
+  </si>
+  <si>
+    <t>App验证企业号-不传QueryType</t>
+  </si>
+  <si>
+    <t>{ "Params": '{"ORGGUID": "#ORGGUID#", "AppName": "com.romens.health.pharmacy.client"}'}</t>
+  </si>
+  <si>
+    <t>{'result': '0001', 'msg': '参数缺失'}</t>
+  </si>
+  <si>
+    <t>App验证企业号-不传Params</t>
+  </si>
+  <si>
+    <t>{"QueryType": "checkOrgCode"}</t>
+  </si>
+  <si>
+    <t>App验证手机号-验证成功</t>
+  </si>
+  <si>
+    <t>{"QueryType": "checkUserPhone", "Params": '{"PHONE":"#PHONE#","ORGGUID": "#ORGGUID#", "AppName": "com.romens.health.pharmacy.client"}'}</t>
+  </si>
+  <si>
+    <t>App验证手机号-手机号为空</t>
+  </si>
+  <si>
+    <t>{"QueryType": "checkUserPhone", "Params": '{"PHONE":"","ORGGUID": "#ORGGUID#", "AppName": "com.romens.health.pharmacy.client"}'}</t>
+  </si>
+  <si>
+    <t>App验证手机号-QueryType为空</t>
+  </si>
+  <si>
+    <t>App验证手机号-AppName为空</t>
+  </si>
+  <si>
+    <t>App验证手机号-不传QueryType</t>
+  </si>
+  <si>
+    <t>App验证手机号-不传Params</t>
+  </si>
+  <si>
+    <t>App验证手机号-企业号为空</t>
+  </si>
+  <si>
+    <t>{"QueryType": "checkUserPhone", "Params": '{"PHONE":"#PHONE#","ORGGUID": "", "AppName": "com.romens.health.pharmacy.client"}'}</t>
+  </si>
+  <si>
+    <t>App验证密码-验证成功</t>
+  </si>
+  <si>
+    <t>{"QueryType": "userLoginInByPwd", "Params": '{"DEVICEID":"#DEVICEID#","USERPHONE":"#PHONE#","PWD":"000000","ORGGUID":"#ORGGUID#","AppName":"com.romens.health.pharmacy.client"}'}</t>
+  </si>
+  <si>
+    <t>App验证密码-密码为空</t>
+  </si>
+  <si>
+    <t>{"QueryType": "userLoginInByPwd", "Params": '{"DEVICEID":"#DEVICEID#","USERPHONE":"#PHONE#","PWD":"","ORGGUID":"#ORGGUID#","AppName":"com.romens.health.pharmacy.client"}'}</t>
+  </si>
+  <si>
+    <t>{'ERROR': '账号或者密码错误，请重试！'}</t>
+  </si>
+  <si>
+    <t>App验证密码-企业号为空</t>
+  </si>
+  <si>
+    <t>{"QueryType": "userLoginInByPwd", "Params": '{"DEVICEID":"#DEVICEID#","USERPHONE":"#PHONE#","PWD":"000000","ORGGUID":"","AppName":"com.romens.health.pharmacy.client"}'}</t>
+  </si>
+  <si>
+    <t>App验证密码-手机号为空</t>
+  </si>
+  <si>
+    <t>{"QueryType": "userLoginInByPwd", "Params": '{"DEVICEID":"#DEVICEID#","USERPHONE":"","PWD":"000000","ORGGUID":"#ORGGUID#","AppName":"com.romens.health.pharmacy.client"}'}</t>
+  </si>
+  <si>
+    <t>App验证密码-设备号为空</t>
+  </si>
+  <si>
+    <t>{"QueryType": "userLoginInByPwd", "Params": '{"DEVICEID":"","USERPHONE":"#PHONE#","PWD":"000000","ORGGUID":"#ORGGUID#","AppName":"com.romens.health.pharmacy.client"}'}</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="2">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="等线"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="等线"/>
+      <charset val="134"/>
+      <family val="3"/>
+      <color rgb="00000000"/>
       <sz val="9"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -121,25 +223,23 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf fontId="0" borderId="0" fillId="0" numFmtId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+  <cellXfs count="4">
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
+    <xf fontId="0" fillId="0" borderId="1" numFmtId="0" xfId="0"/>
+    <xf fontId="0" fillId="0" borderId="1" numFmtId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" builtinId="0" xfId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
 </styleSheet>
 </file>
 
@@ -405,12 +505,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:I7"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15" baseColWidth="10"/>
+  <cols>
+    <col width="7.375" bestFit="1" customWidth="1" style="3" min="1" max="1"/>
+    <col width="8.5" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="27.375" customWidth="1" min="3" max="3"/>
+    <col width="8" bestFit="1" customWidth="1" style="3" min="4" max="4"/>
+    <col width="6.25" bestFit="1" customWidth="1" style="3" min="5" max="5"/>
+    <col width="100.5" customWidth="1" min="6" max="6"/>
+    <col width="42.625" customWidth="1" min="7" max="7"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:9">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
@@ -419,10 +532,10 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
@@ -438,104 +551,188 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A2">
+    <row r="2" spans="1:9">
+      <c r="A2" s="3" t="n">
         <v>1</v>
       </c>
       <c r="B2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" t="s">
         <v>10</v>
       </c>
-      <c r="D2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A3">
+      <c r="D2" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3" s="3" t="n">
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A4">
+        <v>9</v>
+      </c>
+      <c r="C3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4" s="3" t="n">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A5">
+        <v>9</v>
+      </c>
+      <c r="C4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F4" t="s">
+        <v>20</v>
+      </c>
+      <c r="G4" t="s">
+        <v>21</v>
+      </c>
+      <c r="H4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5" s="3" t="n">
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E5" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A6">
+        <v>9</v>
+      </c>
+      <c r="C5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F5" t="s">
+        <v>23</v>
+      </c>
+      <c r="G5" t="s">
+        <v>14</v>
+      </c>
+      <c r="H5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6" s="3" t="n">
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>10</v>
-      </c>
-      <c r="D6" t="s">
-        <v>9</v>
-      </c>
-      <c r="E6" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A7">
+        <v>9</v>
+      </c>
+      <c r="C6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F6" t="s">
+        <v>25</v>
+      </c>
+      <c r="G6" t="s">
+        <v>26</v>
+      </c>
+      <c r="H6" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7" s="3" t="n">
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>10</v>
-      </c>
-      <c r="D7" t="s">
-        <v>9</v>
-      </c>
-      <c r="E7" t="s">
-        <v>11</v>
+        <v>9</v>
+      </c>
+      <c r="C7" t="s">
+        <v>27</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F7" t="s">
+        <v>28</v>
+      </c>
+      <c r="G7" t="s">
+        <v>26</v>
+      </c>
+      <c r="H7" t="s">
+        <v>15</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FAF48E61-3782-48AE-9D01-BA775EC667E1}">
-  <dimension ref="A1:I1"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I8"/>
+  <sheetFormatPr defaultRowHeight="15" baseColWidth="10"/>
+  <cols>
+    <col width="7.375" bestFit="1" customWidth="1" min="1" max="1"/>
+    <col width="8.5" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="27.125" customWidth="1" min="3" max="3"/>
+    <col width="8" bestFit="1" customWidth="1" min="4" max="4"/>
+    <col width="6.25" bestFit="1" customWidth="1" min="5" max="5"/>
+    <col width="120.375" customWidth="1" min="6" max="6"/>
+    <col width="46.125" bestFit="1" customWidth="1" min="7" max="7"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:9">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
@@ -544,10 +741,10 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
@@ -559,23 +756,197 @@
       <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
     </row>
+    <row r="2" spans="1:9">
+      <c r="A2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" t="s">
+        <v>30</v>
+      </c>
+      <c r="G2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F3" t="s">
+        <v>32</v>
+      </c>
+      <c r="G3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F4" t="s">
+        <v>30</v>
+      </c>
+      <c r="G4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" t="s">
+        <v>34</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F5" t="s">
+        <v>30</v>
+      </c>
+      <c r="G5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" t="s">
+        <v>35</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F6" t="s">
+        <v>30</v>
+      </c>
+      <c r="G6" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" t="s">
+        <v>36</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F7" t="s">
+        <v>30</v>
+      </c>
+      <c r="G7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
+      <c r="A8" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" t="s">
+        <v>37</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F8" t="s">
+        <v>38</v>
+      </c>
+      <c r="G8" t="s">
+        <v>18</v>
+      </c>
+    </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4FFAAF2C-ADF0-4CF5-A96F-4611CF41F01E}">
-  <dimension ref="A1:I1"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I6"/>
+  <sheetFormatPr defaultRowHeight="15" baseColWidth="10"/>
+  <cols>
+    <col width="7.375" bestFit="1" customWidth="1" min="1" max="1"/>
+    <col width="8.5" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="27.875" customWidth="1" min="3" max="3"/>
+    <col width="8" bestFit="1" customWidth="1" min="4" max="4"/>
+    <col width="6.25" bestFit="1" customWidth="1" min="5" max="5"/>
+    <col width="150.125" customWidth="1" min="6" max="6"/>
+    <col width="34.75" customWidth="1" min="7" max="7"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:9">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
@@ -584,10 +955,10 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
@@ -599,12 +970,127 @@
       <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
     </row>
+    <row r="2" spans="1:9">
+      <c r="A2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" t="s">
+        <v>40</v>
+      </c>
+      <c r="G2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" t="s">
+        <v>41</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F3" t="s">
+        <v>42</v>
+      </c>
+      <c r="G3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" t="s">
+        <v>44</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F4" t="s">
+        <v>45</v>
+      </c>
+      <c r="G4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" t="s">
+        <v>46</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F5" t="s">
+        <v>47</v>
+      </c>
+      <c r="G5" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" t="s">
+        <v>48</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F6" t="s">
+        <v>49</v>
+      </c>
+      <c r="G6" t="s">
+        <v>14</v>
+      </c>
+    </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
--- a/data/testcase.xlsx
+++ b/data/testcase.xlsx
@@ -3,7 +3,7 @@
 <s:workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:s="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <s:workbookPr codeName="ThisWorkbook"/>
   <s:bookViews>
-    <s:workbookView activeTab="0"/>
+    <s:workbookView activeTab="1"/>
   </s:bookViews>
   <s:sheets>
     <s:sheet name="ORGGUID" sheetId="1" r:id="rId1"/>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="55">
   <si>
     <t>case_id</t>
   </si>
@@ -117,16 +117,31 @@
     <t>{"QueryType": "checkUserPhone", "Params": '{"PHONE":"","ORGGUID": "#ORGGUID#", "AppName": "com.romens.health.pharmacy.client"}'}</t>
   </si>
   <si>
+    <t>未通过</t>
+  </si>
+  <si>
     <t>App验证手机号-QueryType为空</t>
   </si>
   <si>
+    <t>{"QueryType": "", "Params": '{"PHONE":"#PHONE#","ORGGUID": "#ORGGUID#", "AppName": "com.romens.health.pharmacy.client"}'}</t>
+  </si>
+  <si>
     <t>App验证手机号-AppName为空</t>
   </si>
   <si>
+    <t>{"QueryType": "checkUserPhone", "Params": '{"PHONE":"#PHONE#","ORGGUID": "#ORGGUID#", "AppName": ""}'}</t>
+  </si>
+  <si>
     <t>App验证手机号-不传QueryType</t>
   </si>
   <si>
+    <t>{"Params": '{"PHONE":"#PHONE#","ORGGUID": "#ORGGUID#", "AppName": "com.romens.health.pharmacy.client"}'}</t>
+  </si>
+  <si>
     <t>App验证手机号-不传Params</t>
+  </si>
+  <si>
+    <t>{"QueryType": "checkUserPhone"}</t>
   </si>
   <si>
     <t>App验证手机号-企业号为空</t>
@@ -727,7 +742,7 @@
     <col width="27.125" customWidth="1" min="3" max="3"/>
     <col width="8" bestFit="1" customWidth="1" min="4" max="4"/>
     <col width="6.25" bestFit="1" customWidth="1" min="5" max="5"/>
-    <col width="120.375" customWidth="1" min="6" max="6"/>
+    <col width="129.375" customWidth="1" min="6" max="6"/>
     <col width="46.125" bestFit="1" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -782,6 +797,9 @@
       <c r="G2" t="s">
         <v>14</v>
       </c>
+      <c r="H2" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="3" t="n">
@@ -805,6 +823,9 @@
       <c r="G3" t="s">
         <v>18</v>
       </c>
+      <c r="H3" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="3" t="n">
@@ -814,7 +835,7 @@
         <v>9</v>
       </c>
       <c r="C4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>11</v>
@@ -823,10 +844,13 @@
         <v>12</v>
       </c>
       <c r="F4" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="G4" t="s">
         <v>21</v>
+      </c>
+      <c r="H4" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -837,7 +861,7 @@
         <v>9</v>
       </c>
       <c r="C5" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>11</v>
@@ -846,10 +870,13 @@
         <v>12</v>
       </c>
       <c r="F5" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="G5" t="s">
         <v>14</v>
+      </c>
+      <c r="H5" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -860,7 +887,7 @@
         <v>9</v>
       </c>
       <c r="C6" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>11</v>
@@ -869,10 +896,13 @@
         <v>12</v>
       </c>
       <c r="F6" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="G6" t="s">
         <v>26</v>
+      </c>
+      <c r="H6" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -883,7 +913,7 @@
         <v>9</v>
       </c>
       <c r="C7" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>11</v>
@@ -892,10 +922,13 @@
         <v>12</v>
       </c>
       <c r="F7" t="s">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="G7" t="s">
         <v>26</v>
+      </c>
+      <c r="H7" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -906,7 +939,7 @@
         <v>9</v>
       </c>
       <c r="C8" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>11</v>
@@ -915,10 +948,13 @@
         <v>12</v>
       </c>
       <c r="F8" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="G8" t="s">
         <v>18</v>
+      </c>
+      <c r="H8" t="s">
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -941,7 +977,7 @@
     <col width="27.875" customWidth="1" min="3" max="3"/>
     <col width="8" bestFit="1" customWidth="1" min="4" max="4"/>
     <col width="6.25" bestFit="1" customWidth="1" min="5" max="5"/>
-    <col width="150.125" customWidth="1" min="6" max="6"/>
+    <col width="121.875" customWidth="1" min="6" max="6"/>
     <col width="34.75" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -982,7 +1018,7 @@
         <v>9</v>
       </c>
       <c r="C2" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>11</v>
@@ -991,10 +1027,13 @@
         <v>12</v>
       </c>
       <c r="F2" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="G2" t="s">
         <v>14</v>
+      </c>
+      <c r="H2" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -1005,7 +1044,7 @@
         <v>9</v>
       </c>
       <c r="C3" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>11</v>
@@ -1014,10 +1053,13 @@
         <v>12</v>
       </c>
       <c r="F3" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="G3" t="s">
-        <v>43</v>
+        <v>48</v>
+      </c>
+      <c r="H3" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -1028,7 +1070,7 @@
         <v>9</v>
       </c>
       <c r="C4" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>11</v>
@@ -1037,10 +1079,13 @@
         <v>12</v>
       </c>
       <c r="F4" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="G4" t="s">
-        <v>43</v>
+        <v>48</v>
+      </c>
+      <c r="H4" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -1051,7 +1096,7 @@
         <v>9</v>
       </c>
       <c r="C5" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>11</v>
@@ -1060,10 +1105,13 @@
         <v>12</v>
       </c>
       <c r="F5" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="G5" t="s">
-        <v>43</v>
+        <v>48</v>
+      </c>
+      <c r="H5" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -1074,7 +1122,7 @@
         <v>9</v>
       </c>
       <c r="C6" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>11</v>
@@ -1083,10 +1131,13 @@
         <v>12</v>
       </c>
       <c r="F6" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="G6" t="s">
         <v>14</v>
+      </c>
+      <c r="H6" t="s">
+        <v>15</v>
       </c>
     </row>
   </sheetData>

--- a/data/testcase.xlsx
+++ b/data/testcase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Desktop\Romens_Api_Test\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7228AA6B-469C-4622-A969-8D0B5595CEE5}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{607DDB75-C4B0-410D-B981-57952EB8A721}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-3330" yWindow="1545" windowWidth="28800" windowHeight="10455" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ORGGUID" sheetId="1" r:id="rId1"/>
@@ -1191,7 +1191,8 @@
   <cols>
     <col min="2" max="2" width="10" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="23.5" customWidth="1"/>
-    <col min="6" max="6" width="45.75" customWidth="1"/>
+    <col min="6" max="6" width="48" customWidth="1"/>
+    <col min="7" max="7" width="17.5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.2">

--- a/data/testcase.xlsx
+++ b/data/testcase.xlsx
@@ -1,29 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22624"/>
-  <workbookPr codeName="ThisWorkbook"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Desktop\Romens_Api_Test\data\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{607DDB75-C4B0-410D-B981-57952EB8A721}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
-  <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
-  </bookViews>
-  <sheets>
-    <sheet name="ORGGUID" sheetId="1" r:id="rId1"/>
-    <sheet name="PHONE" sheetId="2" r:id="rId2"/>
-    <sheet name="PWD" sheetId="3" r:id="rId3"/>
-    <sheet name="getversion" sheetId="4" r:id="rId4"/>
-  </sheets>
-  <calcPr calcId="0"/>
-</workbook>
+<s:workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:s="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <s:workbookPr codeName="ThisWorkbook"/>
+  <s:bookViews>
+    <s:workbookView activeTab="3"/>
+  </s:bookViews>
+  <s:sheets>
+    <s:sheet name="ORGGUID" sheetId="1" r:id="rId1"/>
+    <s:sheet name="PHONE" sheetId="2" r:id="rId2"/>
+    <s:sheet name="PWD" sheetId="3" r:id="rId3"/>
+    <s:sheet name="getversion" sheetId="4" r:id="rId4"/>
+  </s:sheets>
+  <s:definedNames/>
+  <s:calcPr calcId="124519" fullCalcOnLoad="1"/>
+</s:workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="67">
   <si>
     <t>case_id</t>
   </si>
@@ -52,6 +46,9 @@
     <t>check_sql</t>
   </si>
   <si>
+    <t>checkOrgCode</t>
+  </si>
+  <si>
     <t>App验证企业号-验证成功</t>
   </si>
   <si>
@@ -61,6 +58,9 @@
     <t>/login</t>
   </si>
   <si>
+    <t>{"QueryType": "checkOrgCode", "Params": '{"ORGGUID": "#ORGGUID#", "AppName": "com.romens.health.pharmacy.client"}'}</t>
+  </si>
+  <si>
     <t>{'result': '0000', 'msg': '验证成功'}</t>
   </si>
   <si>
@@ -106,6 +106,9 @@
     <t>{"QueryType": "checkOrgCode"}</t>
   </si>
   <si>
+    <t>checkUserPhone</t>
+  </si>
+  <si>
     <t>App验证手机号-验证成功</t>
   </si>
   <si>
@@ -151,9 +154,15 @@
     <t>{"QueryType": "checkUserPhone", "Params": '{"PHONE":"#PHONE#","ORGGUID": "", "AppName": "com.romens.health.pharmacy.client"}'}</t>
   </si>
   <si>
+    <t>userLoginInByPwd</t>
+  </si>
+  <si>
     <t>App验证密码-验证成功</t>
   </si>
   <si>
+    <t>{"QueryType": "userLoginInByPwd", "Params": '{"DEVICEID":"#DEVICEID#","USERPHONE":"#PHONE#","PWD":"000000","ORGGUID":"#ORGGUID#","AppName":"com.romens.health.pharmacy.client"}'}</t>
+  </si>
+  <si>
     <t>App验证密码-密码为空</t>
   </si>
   <si>
@@ -181,72 +190,61 @@
     <t>{"QueryType": "userLoginInByPwd", "Params": '{"DEVICEID":"","USERPHONE":"#PHONE#","PWD":"000000","ORGGUID":"#ORGGUID#","AppName":"com.romens.health.pharmacy.client"}'}</t>
   </si>
   <si>
-    <t>getversion</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>checkOrgCode</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>checkUserPhone</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>userLoginInByPwd</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>获取app版本信息</t>
-  </si>
-  <si>
-    <t>获取app版本信息-</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <t>getAppVersionAuto</t>
+  </si>
+  <si>
+    <t>获取app版本信息-获取成功</t>
   </si>
   <si>
     <t>/Inquiry</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>post</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{"QueryType": "getAppVersion","Params": '{“type”:”IOS”}'}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{"QueryType": "checkOrgCode", "Params": '{"ORGGUID": "#ORGGUID#", "AppName": "com.romens.health.pharmacy.client"}'}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{"QueryType": "userLoginInByPwd", "Params": '{"DEVICEID":"#DEVICEID#","USERPHONE":"#PHONE#","PWD":"000000","ORGGUID":"#ORGGUID#","AppName":"com.romens.health.pharmacy.client"}'}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"QueryType": "getAppVersionAuto","Params": '{"appId":"com.romens.health.pharmacy.client","clienType":"#clientype#","build":"#build#"}'}</t>
+  </si>
+  <si>
+    <t>{"result": "0000", "msg": "获取成功"}</t>
+  </si>
+  <si>
+    <t>获取app版本信息-clienType为空</t>
+  </si>
+  <si>
+    <t>{"QueryType": "getAppVersionAuto","Params": '{"appId":"com.romens.health.pharmacy.client","clienType":"","build":"#build#"}'}</t>
+  </si>
+  <si>
+    <t>{"result": "0001", "msg": "包名不存在"}</t>
+  </si>
+  <si>
+    <t>获取app版本信息-build为空</t>
+  </si>
+  <si>
+    <t>{"QueryType": "getAppVersionAuto","Params": '{"appId":"com.romens.health.pharmacy.client","clienType":"#clientype#","build":}'}</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="2">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="等线"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="等线"/>
+      <charset val="134"/>
+      <family val="3"/>
+      <color rgb="00000000"/>
       <sz val="9"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -277,31 +275,23 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf fontId="0" borderId="0" fillId="0" numFmtId="0"/>
   </cellStyleXfs>
   <cellXfs count="4">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
+    <xf fontId="0" fillId="0" borderId="1" numFmtId="0" xfId="0"/>
+    <xf fontId="0" fillId="0" borderId="1" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" builtinId="0" xfId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
@@ -567,20 +557,24 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:I7"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="7.375" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.375" customWidth="1"/>
-    <col min="4" max="4" width="8" style="3" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.25" style="3" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="100.5" customWidth="1"/>
-    <col min="7" max="7" width="42.625" customWidth="1"/>
+    <col width="7.375" bestFit="1" customWidth="1" style="3" min="1" max="1"/>
+    <col width="14" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="27.375" customWidth="1" min="3" max="3"/>
+    <col width="8" bestFit="1" customWidth="1" style="3" min="4" max="4"/>
+    <col width="6.25" bestFit="1" customWidth="1" style="3" min="5" max="5"/>
+    <col width="100.5" customWidth="1" min="6" max="6"/>
+    <col width="42.625" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:9">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -609,184 +603,187 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A2" s="3">
+    <row r="2" spans="1:9">
+      <c r="A2" s="3" t="n">
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>53</v>
+        <v>9</v>
       </c>
       <c r="C2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F2" t="s">
-        <v>61</v>
-      </c>
-      <c r="G2" t="s">
-        <v>12</v>
-      </c>
-      <c r="H2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A3" s="3">
-        <v>2</v>
-      </c>
-      <c r="B3" t="s">
-        <v>53</v>
-      </c>
       <c r="C3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F4" t="s">
+        <v>20</v>
+      </c>
+      <c r="G4" t="s">
+        <v>21</v>
+      </c>
+      <c r="H4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F5" t="s">
+        <v>23</v>
+      </c>
+      <c r="G5" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F3" t="s">
-        <v>15</v>
-      </c>
-      <c r="G3" t="s">
-        <v>16</v>
-      </c>
-      <c r="H3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A4" s="3">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>53</v>
-      </c>
-      <c r="C4" t="s">
-        <v>17</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F4" t="s">
-        <v>18</v>
-      </c>
-      <c r="G4" t="s">
-        <v>19</v>
-      </c>
-      <c r="H4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A5" s="3">
-        <v>4</v>
-      </c>
-      <c r="B5" t="s">
-        <v>53</v>
-      </c>
-      <c r="C5" t="s">
-        <v>20</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F5" t="s">
-        <v>21</v>
-      </c>
-      <c r="G5" t="s">
-        <v>12</v>
-      </c>
       <c r="H5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A6" s="3">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6" s="3" t="n">
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>53</v>
+        <v>9</v>
       </c>
       <c r="C6" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G6" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H6" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A7" s="3">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7" s="3" t="n">
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>53</v>
+        <v>9</v>
       </c>
       <c r="C7" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F7" t="s">
+        <v>28</v>
+      </c>
+      <c r="G7" t="s">
         <v>26</v>
       </c>
-      <c r="G7" t="s">
-        <v>24</v>
-      </c>
       <c r="H7" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:I8"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="7.375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.125" customWidth="1"/>
-    <col min="4" max="4" width="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.25" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="129.375" customWidth="1"/>
-    <col min="7" max="7" width="46.125" bestFit="1" customWidth="1"/>
+    <col width="7.375" bestFit="1" customWidth="1" min="1" max="1"/>
+    <col width="15.375" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="27.125" customWidth="1" min="3" max="3"/>
+    <col width="8" bestFit="1" customWidth="1" min="4" max="4"/>
+    <col width="6.25" bestFit="1" customWidth="1" min="5" max="5"/>
+    <col width="129.375" customWidth="1" min="6" max="6"/>
+    <col width="46.125" bestFit="1" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:9">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -815,210 +812,213 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A2" s="3">
+    <row r="2" spans="1:9">
+      <c r="A2" s="3" t="n">
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>54</v>
+        <v>29</v>
       </c>
       <c r="C2" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F2" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="G2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A3" s="3">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3" s="3" t="n">
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>54</v>
+        <v>29</v>
       </c>
       <c r="C3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F3" t="s">
+        <v>33</v>
+      </c>
+      <c r="G3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
         <v>29</v>
       </c>
-      <c r="D3" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F3" t="s">
-        <v>30</v>
-      </c>
-      <c r="G3" t="s">
-        <v>16</v>
-      </c>
-      <c r="H3" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A4" s="3">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>54</v>
-      </c>
       <c r="C4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F4" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="G4" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="H4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A5" s="3">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5" s="3" t="n">
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>54</v>
+        <v>29</v>
       </c>
       <c r="C5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F5" t="s">
+        <v>38</v>
+      </c>
+      <c r="G5" t="s">
+        <v>14</v>
+      </c>
+      <c r="H5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C6" t="s">
+        <v>39</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F6" t="s">
+        <v>40</v>
+      </c>
+      <c r="G6" t="s">
+        <v>26</v>
+      </c>
+      <c r="H6" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>29</v>
+      </c>
+      <c r="C7" t="s">
+        <v>41</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F7" t="s">
+        <v>42</v>
+      </c>
+      <c r="G7" t="s">
+        <v>26</v>
+      </c>
+      <c r="H7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
+      <c r="A8" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>29</v>
+      </c>
+      <c r="C8" t="s">
+        <v>43</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F8" t="s">
+        <v>44</v>
+      </c>
+      <c r="G8" t="s">
+        <v>18</v>
+      </c>
+      <c r="H8" t="s">
         <v>34</v>
       </c>
-      <c r="D5" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F5" t="s">
-        <v>35</v>
-      </c>
-      <c r="G5" t="s">
-        <v>12</v>
-      </c>
-      <c r="H5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A6" s="3">
-        <v>5</v>
-      </c>
-      <c r="B6" t="s">
-        <v>54</v>
-      </c>
-      <c r="C6" t="s">
-        <v>36</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F6" t="s">
-        <v>37</v>
-      </c>
-      <c r="G6" t="s">
-        <v>24</v>
-      </c>
-      <c r="H6" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A7" s="3">
-        <v>6</v>
-      </c>
-      <c r="B7" t="s">
-        <v>54</v>
-      </c>
-      <c r="C7" t="s">
-        <v>38</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F7" t="s">
-        <v>39</v>
-      </c>
-      <c r="G7" t="s">
-        <v>24</v>
-      </c>
-      <c r="H7" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A8" s="3">
-        <v>7</v>
-      </c>
-      <c r="B8" t="s">
-        <v>54</v>
-      </c>
-      <c r="C8" t="s">
-        <v>40</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F8" t="s">
-        <v>41</v>
-      </c>
-      <c r="G8" t="s">
-        <v>16</v>
-      </c>
-      <c r="H8" t="s">
-        <v>31</v>
-      </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:I6"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="7.375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="23.125" customWidth="1"/>
-    <col min="4" max="4" width="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.25" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="121.875" customWidth="1"/>
-    <col min="7" max="7" width="34.75" customWidth="1"/>
+    <col width="7.375" bestFit="1" customWidth="1" min="1" max="1"/>
+    <col width="16.875" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="23.125" customWidth="1" min="3" max="3"/>
+    <col width="8" bestFit="1" customWidth="1" min="4" max="4"/>
+    <col width="6.25" bestFit="1" customWidth="1" min="5" max="5"/>
+    <col width="121.875" customWidth="1" min="6" max="6"/>
+    <col width="34.75" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:9">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1047,155 +1047,158 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A2" s="3">
+    <row r="2" spans="1:9">
+      <c r="A2" s="3" t="n">
         <v>1</v>
       </c>
       <c r="B2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C2" t="s">
+        <v>46</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" t="s">
+        <v>47</v>
+      </c>
+      <c r="G2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F3" t="s">
+        <v>49</v>
+      </c>
+      <c r="G3" t="s">
+        <v>50</v>
+      </c>
+      <c r="H3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>45</v>
+      </c>
+      <c r="C4" t="s">
+        <v>51</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F4" t="s">
+        <v>52</v>
+      </c>
+      <c r="G4" t="s">
+        <v>50</v>
+      </c>
+      <c r="H4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>45</v>
+      </c>
+      <c r="C5" t="s">
+        <v>53</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F5" t="s">
+        <v>54</v>
+      </c>
+      <c r="G5" t="s">
+        <v>50</v>
+      </c>
+      <c r="H5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>45</v>
+      </c>
+      <c r="C6" t="s">
         <v>55</v>
       </c>
-      <c r="C2" t="s">
-        <v>42</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F2" t="s">
-        <v>62</v>
-      </c>
-      <c r="G2" t="s">
-        <v>12</v>
-      </c>
-      <c r="H2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A3" s="3">
-        <v>2</v>
-      </c>
-      <c r="B3" t="s">
-        <v>55</v>
-      </c>
-      <c r="C3" t="s">
-        <v>43</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F3" t="s">
-        <v>44</v>
-      </c>
-      <c r="G3" t="s">
-        <v>45</v>
-      </c>
-      <c r="H3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A4" s="3">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>55</v>
-      </c>
-      <c r="C4" t="s">
-        <v>46</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F4" t="s">
-        <v>47</v>
-      </c>
-      <c r="G4" t="s">
-        <v>45</v>
-      </c>
-      <c r="H4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A5" s="3">
-        <v>4</v>
-      </c>
-      <c r="B5" t="s">
-        <v>55</v>
-      </c>
-      <c r="C5" t="s">
-        <v>48</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F5" t="s">
-        <v>49</v>
-      </c>
-      <c r="G5" t="s">
-        <v>45</v>
-      </c>
-      <c r="H5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A6" s="3">
-        <v>5</v>
-      </c>
-      <c r="B6" t="s">
-        <v>55</v>
-      </c>
-      <c r="C6" t="s">
-        <v>50</v>
-      </c>
       <c r="D6" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F6" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="G6" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H6" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D86C35B6-7E13-4D8B-A8B0-F3EE84993CD0}">
-  <dimension ref="A1:I7"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I4"/>
+  <sheetFormatPr defaultRowHeight="15" baseColWidth="10"/>
   <cols>
-    <col min="2" max="2" width="10" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="23.5" customWidth="1"/>
-    <col min="6" max="6" width="48" customWidth="1"/>
-    <col min="7" max="7" width="17.5" customWidth="1"/>
+    <col width="19.625" customWidth="1" min="2" max="2"/>
+    <col width="28.625" customWidth="1" min="3" max="3"/>
+    <col width="118.625" bestFit="1" customWidth="1" min="6" max="6"/>
+    <col width="31.625" bestFit="1" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:9">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1224,114 +1227,86 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A2" s="3">
+    <row r="2" spans="1:9">
+      <c r="A2" s="3" t="n">
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="C2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" t="s">
         <v>59</v>
-      </c>
-      <c r="E2" t="s">
-        <v>58</v>
       </c>
       <c r="F2" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A3" s="3">
+      <c r="G2" t="s">
+        <v>61</v>
+      </c>
+      <c r="H2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3" s="3" t="n">
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="C3" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="D3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" t="s">
         <v>59</v>
       </c>
-      <c r="E3" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A4" s="3">
+      <c r="F3" t="s">
+        <v>63</v>
+      </c>
+      <c r="G3" t="s">
+        <v>64</v>
+      </c>
+      <c r="H3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4" s="3" t="n">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="C4" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="D4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" t="s">
         <v>59</v>
       </c>
-      <c r="E4" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A5" s="3">
-        <v>4</v>
-      </c>
-      <c r="B5" t="s">
-        <v>52</v>
-      </c>
-      <c r="C5" t="s">
-        <v>56</v>
-      </c>
-      <c r="D5" t="s">
-        <v>59</v>
-      </c>
-      <c r="E5" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A6" s="3">
-        <v>5</v>
-      </c>
-      <c r="B6" t="s">
-        <v>52</v>
-      </c>
-      <c r="C6" t="s">
-        <v>56</v>
-      </c>
-      <c r="D6" t="s">
-        <v>59</v>
-      </c>
-      <c r="E6" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A7" s="3">
-        <v>6</v>
-      </c>
-      <c r="B7" t="s">
-        <v>52</v>
-      </c>
-      <c r="C7" t="s">
-        <v>56</v>
-      </c>
-      <c r="D7" t="s">
-        <v>59</v>
-      </c>
-      <c r="E7" t="s">
-        <v>58</v>
+      <c r="F4" t="s">
+        <v>66</v>
+      </c>
+      <c r="G4" t="s">
+        <v>64</v>
+      </c>
+      <c r="H4" t="s">
+        <v>15</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
--- a/data/testcase.xlsx
+++ b/data/testcase.xlsx
@@ -3,7 +3,7 @@
 <s:workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:s="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <s:workbookPr codeName="ThisWorkbook"/>
   <s:bookViews>
-    <s:workbookView activeTab="3"/>
+    <s:workbookView activeTab="0"/>
   </s:bookViews>
   <s:sheets>
     <s:sheet name="ORGGUID" sheetId="1" r:id="rId1"/>
@@ -112,7 +112,7 @@
     <t>App验证手机号-验证成功</t>
   </si>
   <si>
-    <t>{"QueryType": "checkUserPhone", "Params": '{"PHONE":"#PHONE#","ORGGUID": "#ORGGUID#", "AppName": "com.romens.health.pharmacy.client"}'}</t>
+    <t>{"QueryType": "checkUserPhone", "Params": '{"PHONE":"#USERPHONE#","ORGGUID": "#ORGGUID#", "AppName": "com.romens.health.pharmacy.client"}'}</t>
   </si>
   <si>
     <t>App验证手机号-手机号为空</t>
@@ -127,19 +127,19 @@
     <t>App验证手机号-QueryType为空</t>
   </si>
   <si>
-    <t>{"QueryType": "", "Params": '{"PHONE":"#PHONE#","ORGGUID": "#ORGGUID#", "AppName": "com.romens.health.pharmacy.client"}'}</t>
+    <t>{"QueryType": "", "Params": '{"PHONE":"#USERPHONE#","ORGGUID": "#ORGGUID#", "AppName": "com.romens.health.pharmacy.client"}'}</t>
   </si>
   <si>
     <t>App验证手机号-AppName为空</t>
   </si>
   <si>
-    <t>{"QueryType": "checkUserPhone", "Params": '{"PHONE":"#PHONE#","ORGGUID": "#ORGGUID#", "AppName": ""}'}</t>
+    <t>{"QueryType": "checkUserPhone", "Params": '{"PHONE":"#USERPHONE#","ORGGUID": "#ORGGUID#", "AppName": ""}'}</t>
   </si>
   <si>
     <t>App验证手机号-不传QueryType</t>
   </si>
   <si>
-    <t>{"Params": '{"PHONE":"#PHONE#","ORGGUID": "#ORGGUID#", "AppName": "com.romens.health.pharmacy.client"}'}</t>
+    <t>{"Params": '{"PHONE":"#USERPHONE#","ORGGUID": "#ORGGUID#", "AppName": "com.romens.health.pharmacy.client"}'}</t>
   </si>
   <si>
     <t>App验证手机号-不传Params</t>
@@ -151,7 +151,7 @@
     <t>App验证手机号-企业号为空</t>
   </si>
   <si>
-    <t>{"QueryType": "checkUserPhone", "Params": '{"PHONE":"#PHONE#","ORGGUID": "", "AppName": "com.romens.health.pharmacy.client"}'}</t>
+    <t>{"QueryType": "checkUserPhone", "Params": '{"PHONE":"#USERPHONE#","ORGGUID": "", "AppName": "com.romens.health.pharmacy.client"}'}</t>
   </si>
   <si>
     <t>userLoginInByPwd</t>
@@ -160,13 +160,13 @@
     <t>App验证密码-验证成功</t>
   </si>
   <si>
-    <t>{"QueryType": "userLoginInByPwd", "Params": '{"DEVICEID":"#DEVICEID#","USERPHONE":"#PHONE#","PWD":"000000","ORGGUID":"#ORGGUID#","AppName":"com.romens.health.pharmacy.client"}'}</t>
+    <t>{"QueryType": "userLoginInByPwd", "Params": '{"DEVICEID":"#DEVICEID#","USERPHONE":"#USERPHONE#","PWD":"000000","ORGGUID":"#ORGGUID#","AppName":"com.romens.health.pharmacy.client"}'}</t>
   </si>
   <si>
     <t>App验证密码-密码为空</t>
   </si>
   <si>
-    <t>{"QueryType": "userLoginInByPwd", "Params": '{"DEVICEID":"#DEVICEID#","USERPHONE":"#PHONE#","PWD":"","ORGGUID":"#ORGGUID#","AppName":"com.romens.health.pharmacy.client"}'}</t>
+    <t>{"QueryType": "userLoginInByPwd", "Params": '{"DEVICEID":"#DEVICEID#","USERPHONE":"#USERPHONE#","PWD":"","ORGGUID":"#ORGGUID#","AppName":"com.romens.health.pharmacy.client"}'}</t>
   </si>
   <si>
     <t>{'ERROR': '账号或者密码错误，请重试！'}</t>
@@ -175,7 +175,7 @@
     <t>App验证密码-企业号为空</t>
   </si>
   <si>
-    <t>{"QueryType": "userLoginInByPwd", "Params": '{"DEVICEID":"#DEVICEID#","USERPHONE":"#PHONE#","PWD":"000000","ORGGUID":"","AppName":"com.romens.health.pharmacy.client"}'}</t>
+    <t>{"QueryType": "userLoginInByPwd", "Params": '{"DEVICEID":"#DEVICEID#","USERPHONE":"#USERPHONE#","PWD":"000000","ORGGUID":"","AppName":"com.romens.health.pharmacy.client"}'}</t>
   </si>
   <si>
     <t>App验证密码-手机号为空</t>
@@ -187,7 +187,7 @@
     <t>App验证密码-设备号为空</t>
   </si>
   <si>
-    <t>{"QueryType": "userLoginInByPwd", "Params": '{"DEVICEID":"","USERPHONE":"#PHONE#","PWD":"000000","ORGGUID":"#ORGGUID#","AppName":"com.romens.health.pharmacy.client"}'}</t>
+    <t>{"QueryType": "userLoginInByPwd", "Params": '{"DEVICEID":"","USERPHONE":"#USERPHONE#","PWD":"000000","ORGGUID":"#ORGGUID#","AppName":"com.romens.health.pharmacy.client"}'}</t>
   </si>
   <si>
     <t>getAppVersionAuto</t>
@@ -1014,7 +1014,7 @@
     <col width="23.125" customWidth="1" min="3" max="3"/>
     <col width="8" bestFit="1" customWidth="1" min="4" max="4"/>
     <col width="6.25" bestFit="1" customWidth="1" min="5" max="5"/>
-    <col width="121.875" customWidth="1" min="6" max="6"/>
+    <col width="174" bestFit="1" customWidth="1" min="6" max="6"/>
     <col width="34.75" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -1192,9 +1192,11 @@
   <dimension ref="A1:I4"/>
   <sheetFormatPr defaultRowHeight="15" baseColWidth="10"/>
   <cols>
-    <col width="19.625" customWidth="1" min="2" max="2"/>
+    <col width="17.375" customWidth="1" min="2" max="2"/>
     <col width="28.625" customWidth="1" min="3" max="3"/>
-    <col width="118.625" bestFit="1" customWidth="1" min="6" max="6"/>
+    <col width="8" bestFit="1" customWidth="1" min="4" max="4"/>
+    <col width="7.75" bestFit="1" customWidth="1" min="5" max="5"/>
+    <col width="111.5" customWidth="1" min="6" max="6"/>
     <col width="31.625" bestFit="1" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>

--- a/data/testcase.xlsx
+++ b/data/testcase.xlsx
@@ -3,13 +3,15 @@
 <s:workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:s="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <s:workbookPr codeName="ThisWorkbook"/>
   <s:bookViews>
-    <s:workbookView activeTab="0"/>
+    <s:workbookView activeTab="5"/>
   </s:bookViews>
   <s:sheets>
     <s:sheet name="ORGGUID" sheetId="1" r:id="rId1"/>
     <s:sheet name="PHONE" sheetId="2" r:id="rId2"/>
     <s:sheet name="PWD" sheetId="3" r:id="rId3"/>
     <s:sheet name="getversion" sheetId="4" r:id="rId4"/>
+    <s:sheet name="getFileUploadParams" sheetId="5" r:id="rId5"/>
+    <s:sheet name="getTxCosConfig" sheetId="6" r:id="rId6"/>
   </s:sheets>
   <s:definedNames/>
   <s:calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="78">
   <si>
     <t>case_id</t>
   </si>
@@ -218,6 +220,39 @@
   </si>
   <si>
     <t>{"QueryType": "getAppVersionAuto","Params": '{"appId":"com.romens.health.pharmacy.client","clienType":"#clientype#","build":}'}</t>
+  </si>
+  <si>
+    <t>getFileUploadParams</t>
+  </si>
+  <si>
+    <t>获取上传参数-获取成功</t>
+  </si>
+  <si>
+    <t>{"QueryType": "getFileUploadParams","Params": 'params'}</t>
+  </si>
+  <si>
+    <t>获取上传参数-Params为空</t>
+  </si>
+  <si>
+    <t>{"QueryType": "getFileUploadParams","Params": ''}</t>
+  </si>
+  <si>
+    <t>getTxCosConfig</t>
+  </si>
+  <si>
+    <t>获取腾讯COS临时参数-获取成功</t>
+  </si>
+  <si>
+    <t>{"QueryType": "getTxCosConfig","Params": 'params'}</t>
+  </si>
+  <si>
+    <t>{"result": "0000", "msg": "成功"}</t>
+  </si>
+  <si>
+    <t>获取腾讯COS临时参数-Params为空</t>
+  </si>
+  <si>
+    <t>{"QueryType": "getTxCosConfig","Params": ''}</t>
   </si>
 </sst>
 </file>
@@ -1311,4 +1346,213 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I3"/>
+  <sheetFormatPr defaultRowHeight="15" baseColWidth="10"/>
+  <cols>
+    <col width="7.375" bestFit="1" customWidth="1" style="3" min="1" max="1"/>
+    <col width="18.625" customWidth="1" min="2" max="2"/>
+    <col width="25" bestFit="1" customWidth="1" min="3" max="3"/>
+    <col width="8" bestFit="1" customWidth="1" min="4" max="4"/>
+    <col width="7.75" bestFit="1" customWidth="1" min="5" max="5"/>
+    <col width="47.75" customWidth="1" min="6" max="6"/>
+    <col width="29.75" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" t="s">
+        <v>59</v>
+      </c>
+      <c r="F2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G2" t="s">
+        <v>61</v>
+      </c>
+      <c r="H2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>67</v>
+      </c>
+      <c r="C3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F3" t="s">
+        <v>71</v>
+      </c>
+      <c r="G3" t="s">
+        <v>61</v>
+      </c>
+      <c r="H3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I3"/>
+  <sheetFormatPr defaultRowHeight="15" baseColWidth="10"/>
+  <cols>
+    <col width="14.125" customWidth="1" min="2" max="2"/>
+    <col width="33" bestFit="1" customWidth="1" min="3" max="3"/>
+    <col width="8" bestFit="1" customWidth="1" min="4" max="4"/>
+    <col width="7.75" bestFit="1" customWidth="1" min="5" max="5"/>
+    <col width="43.75" customWidth="1" min="6" max="6"/>
+    <col width="31.625" bestFit="1" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>72</v>
+      </c>
+      <c r="C2" t="s">
+        <v>73</v>
+      </c>
+      <c r="D2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" t="s">
+        <v>59</v>
+      </c>
+      <c r="F2" t="s">
+        <v>74</v>
+      </c>
+      <c r="G2" t="s">
+        <v>75</v>
+      </c>
+      <c r="H2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C3" t="s">
+        <v>76</v>
+      </c>
+      <c r="D3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F3" t="s">
+        <v>77</v>
+      </c>
+      <c r="G3" t="s">
+        <v>75</v>
+      </c>
+      <c r="H3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9"/>
+</worksheet>
 </file>
--- a/data/testcase.xlsx
+++ b/data/testcase.xlsx
@@ -12,6 +12,9 @@
     <s:sheet name="getversion" sheetId="4" r:id="rId4"/>
     <s:sheet name="getFileUploadParams" sheetId="5" r:id="rId5"/>
     <s:sheet name="getTxCosConfig" sheetId="6" r:id="rId6"/>
+    <s:sheet name="syncSysConfig" sheetId="7" r:id="rId7"/>
+    <s:sheet name="getConfig" sheetId="8" r:id="rId8"/>
+    <s:sheet name="getAppTitle" sheetId="9" r:id="rId9"/>
   </s:sheets>
   <s:definedNames/>
   <s:calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="87">
   <si>
     <t>case_id</t>
   </si>
@@ -253,6 +256,33 @@
   </si>
   <si>
     <t>{"QueryType": "getTxCosConfig","Params": ''}</t>
+  </si>
+  <si>
+    <t>syncSysConfig</t>
+  </si>
+  <si>
+    <t>获取系统配置-获取成功</t>
+  </si>
+  <si>
+    <t>{"QueryType": "syncSysConfig","Params": '{"LASTTIME":0}'}</t>
+  </si>
+  <si>
+    <t>getConfig</t>
+  </si>
+  <si>
+    <t>获取配置-获取成功</t>
+  </si>
+  <si>
+    <t>{"QueryType": "getConfig","Params": ''}</t>
+  </si>
+  <si>
+    <t>getAppTitle</t>
+  </si>
+  <si>
+    <t>获取首页功能模块-获取成功</t>
+  </si>
+  <si>
+    <t>{"QueryType": "getAppTitle","Params": ''}</t>
   </si>
 </sst>
 </file>
@@ -1555,4 +1585,233 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I2"/>
+  <sheetFormatPr defaultRowHeight="15" baseColWidth="10"/>
+  <cols>
+    <col width="14.875" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="20.625" customWidth="1" min="3" max="3"/>
+    <col width="8" bestFit="1" customWidth="1" min="4" max="4"/>
+    <col width="7.75" bestFit="1" customWidth="1" min="5" max="5"/>
+    <col width="51.375" bestFit="1" customWidth="1" min="6" max="6"/>
+    <col width="27.5" bestFit="1" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>78</v>
+      </c>
+      <c r="C2" t="s">
+        <v>79</v>
+      </c>
+      <c r="D2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" t="s">
+        <v>59</v>
+      </c>
+      <c r="F2" t="s">
+        <v>80</v>
+      </c>
+      <c r="G2" t="s">
+        <v>61</v>
+      </c>
+      <c r="H2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I2"/>
+  <sheetFormatPr defaultRowHeight="15" baseColWidth="10"/>
+  <cols>
+    <col width="14.875" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="18.375" bestFit="1" customWidth="1" min="3" max="3"/>
+    <col width="8" bestFit="1" customWidth="1" min="4" max="4"/>
+    <col width="34.375" bestFit="1" customWidth="1" min="6" max="6"/>
+    <col width="27.5" bestFit="1" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" t="s">
+        <v>59</v>
+      </c>
+      <c r="F2" t="s">
+        <v>83</v>
+      </c>
+      <c r="G2" t="s">
+        <v>61</v>
+      </c>
+      <c r="H2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I2"/>
+  <sheetFormatPr defaultRowHeight="15" baseColWidth="10"/>
+  <cols>
+    <col width="14.875" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="26.625" bestFit="1" customWidth="1" min="3" max="3"/>
+    <col width="7.75" bestFit="1" customWidth="1" min="5" max="5"/>
+    <col width="36.25" bestFit="1" customWidth="1" min="6" max="6"/>
+    <col width="27.5" bestFit="1" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C2" t="s">
+        <v>85</v>
+      </c>
+      <c r="D2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" t="s">
+        <v>59</v>
+      </c>
+      <c r="F2" t="s">
+        <v>86</v>
+      </c>
+      <c r="G2" t="s">
+        <v>61</v>
+      </c>
+      <c r="H2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>